--- a/static/TEMPLATE_IMPORT.xlsx
+++ b/static/TEMPLATE_IMPORT.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20148" windowHeight="7044"/>
+    <workbookView windowWidth="23028" windowHeight="9395"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>epc</t>
   </si>
   <si>
     <t>bib</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
   <si>
     <t>E28011702000100587AA0B1B</t>
@@ -1227,23 +1236,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="28.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>123</v>
@@ -1251,7 +1269,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>456</v>
@@ -1259,7 +1277,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>789</v>
@@ -1267,7 +1285,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1122</v>
@@ -1275,7 +1293,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>1455</v>
@@ -1283,7 +1301,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1788</v>
@@ -1291,7 +1309,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>2121</v>
@@ -1299,7 +1317,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>2454</v>
@@ -1307,7 +1325,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>2787</v>
@@ -1315,7 +1333,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>3120</v>
@@ -1323,7 +1341,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>3453</v>
@@ -1331,7 +1349,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>3786</v>
@@ -1339,7 +1357,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>4119</v>
@@ -1347,7 +1365,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>4452</v>

--- a/static/TEMPLATE_IMPORT.xlsx
+++ b/static/TEMPLATE_IMPORT.xlsx
@@ -8,19 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB329\IDLAPS CHECKPOINT\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C95A247-7AF7-4A95-A37F-36C714CFA323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844C298F-C1B0-414E-9702-9FFDC722BCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="category" sheetId="2" r:id="rId1"/>
+    <sheet name="epc" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>epc</t>
   </si>
@@ -77,6 +83,12 @@
   </si>
   <si>
     <t>category_id</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>lap</t>
   </si>
 </sst>
 </file>
@@ -605,6 +617,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFECD702-9DCA-4B1F-9915-FB173D90B7BF}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
